--- a/histograms/histogram_avg_p_valence_electrons.xlsx
+++ b/histograms/histogram_avg_p_valence_electrons.xlsx
@@ -445,7 +445,7 @@
         <v>1.0625</v>
       </c>
       <c r="B2" t="n">
-        <v>1149</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>1.1875</v>
       </c>
       <c r="B3" t="n">
-        <v>1026</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>1.3125</v>
       </c>
       <c r="B4" t="n">
-        <v>2547</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>1.4375</v>
       </c>
       <c r="B5" t="n">
-        <v>446</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>1.5625</v>
       </c>
       <c r="B6" t="n">
-        <v>736</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>1.6875</v>
       </c>
       <c r="B7" t="n">
-        <v>316</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>1.8125</v>
       </c>
       <c r="B8" t="n">
-        <v>170</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -525,7 +525,7 @@
         <v>2.3125</v>
       </c>
       <c r="B12" t="n">
-        <v>5700</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>2.4375</v>
       </c>
       <c r="B13" t="n">
-        <v>2194</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>2.5625</v>
       </c>
       <c r="B14" t="n">
-        <v>7737</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>2.6875</v>
       </c>
       <c r="B15" t="n">
-        <v>2024</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>2.8125</v>
       </c>
       <c r="B16" t="n">
-        <v>58</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -573,7 +573,7 @@
         <v>3.0625</v>
       </c>
       <c r="B18" t="n">
-        <v>155</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>3.1875</v>
       </c>
       <c r="B19" t="n">
-        <v>1856</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -597,7 +597,7 @@
         <v>3.4375</v>
       </c>
       <c r="B21" t="n">
-        <v>285</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
